--- a/gross_per_show_cutoff_comp.xlsx
+++ b/gross_per_show_cutoff_comp.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -603,68 +603,68 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Stadium</t>
+          <t>Amphitheatre</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
         <v>2024</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2822097</v>
+        <v>523794</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2646704</v>
+        <v>474889</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3316775</v>
+        <v>554662</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>3633140</v>
+        <v>574020</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>114.42</v>
+        <v>66.89</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>106.02</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>24663.9</v>
+        <v>7830.7</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>24963.8</v>
+        <v>6713.2</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>1044</v>
+        <v>1629</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>381</v>
+        <v>709</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>1227</v>
+        <v>1725</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>523</v>
+        <v>857</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>30262559</v>
+        <v>13508033</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>13056078</v>
+        <v>5753255</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>3462712841.11</v>
+        <v>903543804.24</v>
       </c>
       <c r="S3" s="3" t="n">
-        <v>1384226380.11</v>
+        <v>406979931.82</v>
       </c>
       <c r="T3" s="4" t="n">
-        <v>-0.0621</v>
+        <v>-0.0934</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>-0.07340000000000001</v>
+        <v>0.0576</v>
       </c>
       <c r="V3" s="4" t="n">
-        <v>0.0122</v>
+        <v>-0.1427</v>
       </c>
     </row>
     <row r="4">
@@ -675,68 +675,68 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Stadium</t>
+          <t>Amphitheatre</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
         <v>2025</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3490521</v>
+        <v>480371</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2897575</v>
+        <v>507385</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>4241137</v>
+        <v>503196</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>3953340</v>
+        <v>543565</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>126.31</v>
+        <v>66.81</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>112.4</v>
+        <v>72.31</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>27634.2</v>
+        <v>7190.1</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>25779</v>
+        <v>7017.2</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1130</v>
+        <v>1389</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>376</v>
+        <v>589</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1373</v>
+        <v>1455</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>513</v>
+        <v>631</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>37941736</v>
+        <v>10461654</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>13224629</v>
+        <v>4427829</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>4792484999.16</v>
+        <v>698939561.02</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>1486455936.9</v>
+        <v>320159724.61</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>-0.1699</v>
+        <v>0.0562</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>-0.1101</v>
+        <v>0.0823</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>-0.06710000000000001</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="5">
@@ -747,68 +747,68 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Amphitheatre</t>
+          <t>Stadium</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
         <v>2024</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>523794</v>
+        <v>2814214</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>474889</v>
+        <v>2646704</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>554662</v>
+        <v>3305627</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>574020</v>
+        <v>3633140</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>66.89</v>
+        <v>114.35</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>70.73999999999999</v>
+        <v>106.02</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>7830.7</v>
+        <v>24610.9</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>6713.2</v>
+        <v>24963.8</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1629</v>
+        <v>1048</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>709</v>
+        <v>381</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>1725</v>
+        <v>1231</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>857</v>
+        <v>523</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>13508033</v>
+        <v>30296051</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>5753255</v>
+        <v>13056078</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>903543804.24</v>
+        <v>3464296974.5</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>406979931.82</v>
+        <v>1384226380.11</v>
       </c>
       <c r="T5" s="4" t="n">
-        <v>-0.0934</v>
+        <v>-0.0595</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0.0576</v>
+        <v>-0.0728</v>
       </c>
       <c r="V5" s="4" t="n">
-        <v>-0.1427</v>
+        <v>0.0143</v>
       </c>
     </row>
     <row r="6">
@@ -819,68 +819,68 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Amphitheatre</t>
+          <t>Stadium</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
         <v>2025</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>480371</v>
+        <v>3487999</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>507782</v>
+        <v>2897575</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>503196</v>
+        <v>4237410</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>544052</v>
+        <v>3953340</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>66.81</v>
+        <v>126.31</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>72.31999999999999</v>
+        <v>112.4</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>7190.1</v>
+        <v>27614.6</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>7021.6</v>
+        <v>25779</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>1389</v>
+        <v>1131</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>588</v>
+        <v>376</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>1455</v>
+        <v>1374</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>630</v>
+        <v>513</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>10461654</v>
+        <v>37942458</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>4423614</v>
+        <v>13224629</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>698939561.02</v>
+        <v>4792510244.32</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>319902481.61</v>
+        <v>1486455936.9</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.0571</v>
+        <v>-0.1693</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.0825</v>
+        <v>-0.1101</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.0234</v>
+        <v>-0.0665</v>
       </c>
     </row>
     <row r="7">
@@ -891,68 +891,68 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Arena</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
         <v>2024</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1479084</v>
+        <v>736276</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1297976</v>
+        <v>688772</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1633467</v>
+        <v>948653</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1643309</v>
+        <v>827975</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>99.75</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>95.23</v>
+        <v>90.03</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14827.4</v>
+        <v>7666.7</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>13630</v>
+        <v>7650.2</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>2673</v>
+        <v>5644</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1090</v>
+        <v>3993</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>2952</v>
+        <v>7272</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1380</v>
+        <v>4800</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>43770592</v>
+        <v>55752318</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>18809333</v>
+        <v>36721156</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>4366256645.35</v>
+        <v>5354196309.34</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>1791206311.93</v>
+        <v>3306103290.62</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.1224</v>
+        <v>-0.0645</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-0.0453</v>
+        <v>-0.0626</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.0808</v>
+        <v>-0.0022</v>
       </c>
     </row>
     <row r="8">
@@ -963,500 +963,1652 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Arena</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
         <v>2025</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1941805</v>
+        <v>717993</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1580366</v>
+        <v>779913</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2180002</v>
+        <v>883610</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1873816</v>
+        <v>923209</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>113.45</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>102.35</v>
+        <v>91.7</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>17115.8</v>
+        <v>7800.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>15440.3</v>
+        <v>8505</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>2519</v>
+        <v>5276</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>964</v>
+        <v>3750</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>2828</v>
+        <v>6493</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>1143</v>
+        <v>4439</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>48403390</v>
+        <v>50650580</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>17648243</v>
+        <v>37753708</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>5491424560.18</v>
+        <v>4661928547.74</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1806358418.51</v>
+        <v>3462032049.73</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.1861</v>
+        <v>0.0862</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.0978</v>
+        <v>-0.0037</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.0979</v>
+        <v>0.09030000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>LiveNation</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Stadium</t>
+          <t>Theater</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
         <v>2024</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>4586633</v>
+        <v>108860</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5200285</v>
+        <v>106580</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5878015</v>
+        <v>140251</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6465219</v>
+        <v>141790</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>121.78</v>
+        <v>69.03</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>123.48</v>
+        <v>70.86</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>37662.8</v>
+        <v>1577</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>42114.7</v>
+        <v>1504</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>206</v>
+        <v>13046</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>111</v>
+        <v>9187</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>264</v>
+        <v>16808</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>138</v>
+        <v>12222</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>9942975</v>
+        <v>26505933</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>5811832</v>
+        <v>18381785</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1210871081.01</v>
+        <v>1829710810.81</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>717639266.29</v>
+        <v>1302620453.81</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.1338</v>
+        <v>-0.0209</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.014</v>
+        <v>0.0265</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.1182</v>
+        <v>-0.0463</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>LiveNation</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Stadium</t>
+          <t>Theater</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
         <v>2025</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>6212065</v>
+        <v>106536</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>5202382</v>
+        <v>115486</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>8153335</v>
+        <v>135221</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>6470189</v>
+        <v>149693</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>145.96</v>
+        <v>71.39</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>126.38</v>
+        <v>74.75</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>42560.1</v>
+        <v>1492.3</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>41164.1</v>
+        <v>1545</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>368</v>
+        <v>13359</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>119</v>
+        <v>8788</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>483</v>
+        <v>16956</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>148</v>
+        <v>11391</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>20556542</v>
+        <v>25304100</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>6092282</v>
+        <v>17599038</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>3000427428.5</v>
+        <v>1806417103.97</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>769952463.3099999</v>
+        <v>1315500274.67</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.1625</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.1341</v>
+        <v>0.0471</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.0328</v>
+        <v>0.0353</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>LiveNation</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Amphitheatre</t>
+          <t>Club</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
         <v>2024</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>729365</v>
+        <v>21901</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>759504</v>
+        <v>25050</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>756819</v>
+        <v>22824</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>789065</v>
+        <v>25830</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>65.25</v>
+        <v>40.03</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>69.97</v>
+        <v>42.7</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>11177.6</v>
+        <v>547.1</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>10855.3</v>
+        <v>586.6</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>797</v>
+        <v>15081</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>334</v>
+        <v>8956</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>827</v>
+        <v>15716</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>347</v>
+        <v>9235</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>9243903</v>
+        <v>8598514</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>3766778</v>
+        <v>5417496</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>603185039.86</v>
+        <v>344201437.43</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>263547808.85</v>
+        <v>231337666.35</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.0413</v>
+        <v>0.1438</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.0723</v>
+        <v>0.0667</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.0288</v>
+        <v>0.0722</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>LiveNation</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Amphitheatre</t>
+          <t>Club</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
         <v>2025</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>647028</v>
+        <v>22907</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>683383</v>
+        <v>25846</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>664055</v>
+        <v>23803</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>717431</v>
+        <v>26874</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>62.98</v>
+        <v>42.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>69.90000000000001</v>
+        <v>44.64</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>10273.2</v>
+        <v>537.7</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>9776.4</v>
+        <v>578.9</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>646</v>
+        <v>13602</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>281</v>
+        <v>7593</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>663</v>
+        <v>14134</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>295</v>
+        <v>7895</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>6811144</v>
+        <v>7600436</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>2884052</v>
+        <v>4570574</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>428979388.41</v>
+        <v>323763441.39</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>201598051.24</v>
+        <v>204053161.99</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.0562</v>
+        <v>0.1283</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.1099</v>
+        <v>0.0479</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.0484</v>
+        <v>0.0766</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>LiveNation</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
         <v>2024</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1662746</v>
+        <v>238041</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2023066</v>
+        <v>111855</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1808630</v>
+        <v>258596</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>2204915</v>
+        <v>133674</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>94.55</v>
+        <v>75.86</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>102.44</v>
+        <v>63.08</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>17586.5</v>
+        <v>3137.8</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>19749.7</v>
+        <v>1773.3</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>1003</v>
+        <v>2513</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>445</v>
+        <v>1338</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>1091</v>
+        <v>2730</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>485</v>
+        <v>1599</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>19186878</v>
+        <v>8566101</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>9578610</v>
+        <v>2835506</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>1814056120.87</v>
+        <v>649851513</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>981187075.14</v>
+        <v>178855982.14</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.2167</v>
+        <v>-0.5301</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.0834</v>
+        <v>-0.1685</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.123</v>
+        <v>-0.4349</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>LiveNation</t>
+          <t>Market</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
         <v>2025</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2992502</v>
+        <v>231171</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2193116</v>
+        <v>211538</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>3382058</v>
+        <v>277462</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>2428876</v>
+        <v>230612</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>125.31</v>
+        <v>86.78</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>108.23</v>
+        <v>81.59</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>23881.1</v>
+        <v>2663.9</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>20262.6</v>
+        <v>2592.8</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1014</v>
+        <v>2412</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>400</v>
+        <v>1220</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>1146</v>
+        <v>2895</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>443</v>
+        <v>1330</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>27367686</v>
+        <v>7712077</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>8976334</v>
+        <v>3448424</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>3429406816.91</v>
+        <v>669238917.8099999</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>971550514.55</v>
+        <v>281346113.63</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.2671</v>
+        <v>-0.0849</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.1363</v>
+        <v>-0.0598</v>
       </c>
       <c r="V14" s="4" t="n">
+        <v>-0.0267</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>275841</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>232936</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>322009</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>277240</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>87.59</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>82.88</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>3149.1</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>2810.4</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>38961</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>24564</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>45482</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>29236</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>143226950</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>82165276</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>12545800849.32</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>6810123704.85</v>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>-0.1555</v>
+      </c>
+      <c r="U15" s="4" t="n">
+        <v>-0.0538</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>-0.1076</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>299092</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>269840</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>348484</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>316793</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>92.73999999999999</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>3225.1</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>3092.6</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>37169</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>22316</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>26199</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>139671305</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>81024202</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>12952797816.25</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>7069547261.53</v>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>-0.0978</v>
+      </c>
+      <c r="U16" s="4" t="n">
+        <v>-0.0592</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>-0.0411</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>LiveNation</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>729365</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>759504</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>756819</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>789065</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>69.97</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>11177.6</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>10855.3</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>797</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>334</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>827</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>347</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>9243903</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>3766778</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>603185039.86</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>263547808.85</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>0.0413</v>
+      </c>
+      <c r="U17" s="4" t="n">
+        <v>0.0723</v>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>-0.0288</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>LiveNation</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Amphitheatre</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>647028</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>681944</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>664055</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>715799</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>62.98</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>69.89</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>10273.2</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>9757.700000000001</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>646</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>282</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>663</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>296</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>6811144</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>2888267</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>428979388.41</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>201855294.24</v>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>-0.0502</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>LiveNation</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>4586633</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>5200285</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>5878015</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>6465219</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>121.78</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>123.48</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>37662.8</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>42114.7</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>206</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>9942975</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>5811832</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>1210871081.01</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>717639266.29</v>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>0.1338</v>
+      </c>
+      <c r="U19" s="4" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>0.1182</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>LiveNation</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Stadium</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>6212065</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>5202382</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>8153335</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>6470189</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>145.96</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>126.38</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>42560.1</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>41164.1</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>368</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>483</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>20556542</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>6092282</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>3000427428.5</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>769952463.3099999</v>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>-0.1625</v>
+      </c>
+      <c r="U20" s="4" t="n">
+        <v>-0.1341</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>-0.0328</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>LiveNation</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1384801</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>1125284</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>1555317</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>1256648</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>130.96</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>111.12</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>10574.6</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>10126.8</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>1608</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>1165</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>1806</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>1301</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>19097696</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>13174980</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>2500949906.61</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>1463994734</v>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>-0.1874</v>
+      </c>
+      <c r="U21" s="4" t="n">
         <v>-0.1515</v>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>-0.0423</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>LiveNation</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Arena</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1215271</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>1108463</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>1329975</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>1245154</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>116.39</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>110.04</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>10441.4</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>10072.9</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>1229</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>965</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>1345</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>1084</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>14043732</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>10918998</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>1634539612.31</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>1201573658.64</v>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>-0.08790000000000001</v>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>-0.0546</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>-0.0353</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>LiveNation</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>191089</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>177217</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>219416</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>196019</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>86.73999999999999</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>83.37</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>2203.1</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>2125.8</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>1248</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>886</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1433</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>980</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>3156999</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>2083241</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>273831139.93</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>173673025.16</v>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>-0.0726</v>
+      </c>
+      <c r="U23" s="4" t="n">
+        <v>-0.0389</v>
+      </c>
+      <c r="V23" s="4" t="n">
+        <v>-0.0351</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>LiveNation</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>179668</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>168936</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>196720</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>192274</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>84.04000000000001</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>81.31</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>2138</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>2077.7</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>1159</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>789</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>1269</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>898</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>2713110</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>1865813</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>227998562.64</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>151704349.46</v>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>-0.0597</v>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>-0.0325</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>-0.0282</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>LiveNation</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>54991</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>62743</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>56544</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>64174</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>1132.9</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>1148.4</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>570</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>874</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>583</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>990168</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>669542</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>48062548.65</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>36579334.52</v>
+      </c>
+      <c r="T25" s="4" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="U25" s="4" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>0.0137</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>LiveNation</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Club</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>55976</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>50586</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>57274</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>51396</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>1130.1</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>1039.9</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>863</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>562</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>883</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>571</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>997874</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>593767</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>49427128.85</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>28884763.54</v>
+      </c>
+      <c r="T26" s="4" t="n">
+        <v>-0.0963</v>
+      </c>
+      <c r="U26" s="4" t="n">
+        <v>-0.0178</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>-0.0798</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>LiveNation</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>664924</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>269244</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>678493</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>280308</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>91.73999999999999</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>73.36</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>7248.2</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>3670.3</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>724821</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>278943</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>66492361.81</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>20462509</v>
+      </c>
+      <c r="T27" s="4" t="n">
+        <v>-0.5951</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>-0.2003</v>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>-0.4936</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>LiveNation</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>645016</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>615375</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>651666</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>669355</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>119.98</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>7064.7</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>5128.9</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>692340</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>317992</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>63211600.47</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>38153256.14</v>
+      </c>
+      <c r="T28" s="4" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>-0.274</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>LiveNation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>886763</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>781284</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>978446</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>852468</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>108.98</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>103.78</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>8136.6</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>7528.6</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>4807</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>3139</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>5304</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>3425</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>43156562</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>25785316</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>4703392077.87</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>2675896677.82</v>
+      </c>
+      <c r="T29" s="4" t="n">
+        <v>-0.1189</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>-0.0477</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>-0.0747</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>LiveNation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1139967</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>781995</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>1239015</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>862337</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>117.97</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>105.49</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>9663.5</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>7413.2</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>4362</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>2774</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>4741</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>3059</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>45814742</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>22677119</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>5404583721.18</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>2392123785.33</v>
+      </c>
+      <c r="T30" s="4" t="n">
+        <v>-0.314</v>
+      </c>
+      <c r="U30" s="4" t="n">
+        <v>-0.1058</v>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>-0.2329</v>
       </c>
     </row>
   </sheetData>
@@ -1470,7 +2622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1497,101 +2649,125 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Gross per show = SUM(grossUSD) / SUM(numShows) for one basis x year x pre/post cell. grossUSD is a whole-run total (verified: grossUSD = avgGrossUSD * numShows).</t>
+          <t>Gross per show = SUM(grossUSD) / SUM(numShows) for one basis x category x year x pre/post cell. grossUSD is a whole-run total (verified: grossUSD = avgGrossUSD * numShows).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Cutoff</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>PRE = eventDate on or before Aug 25 of the show year; POST = after.</t>
+          <t>The six pipeline categories from post_aug25_capacity.py: Amphitheatre, Stadium, Arena, Theater, Club, Other. 'All' adds the six.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Other bucket</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>pollstar/concerts.csv (data ends 2026-08-16). 2024 and 2025 settled both sides.</t>
+          <t>Pollstar has 13 companyType values; this taxonomy keeps five. Casino, Convention Center, Complex, Outdoor Venues, Festival, Theme Park, Streaming Online and Promoter all fall to Other. A large Other is a sign the taxonomy does not fit the source, not a data error.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Grain</t>
+          <t>Cutoff</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>ONE ROW = ONE ENGAGEMENT. numShows = performances inside it.</t>
+          <t>PRE = eventDate on or before Aug 25 of the show year; POST = after.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Why per-show moved</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Gross per show = avg ticket price x tickets per show. The two change % columns decompose the move into a price and a volume effect.</t>
+          <t>pollstar/concerts.csv (data ends 2026-08-16). 2024 and 2025 settled both sides.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mix caveat</t>
+          <t>Grain</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>POST Aug 25 is the tail of the season, so act/venue mix shifts. Compare Stadium vs Amphitheatre and LiveNation vs Market before concluding.</t>
+          <t>ONE ROW = ONE ENGAGEMENT. numShows = performances inside it.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Live Nation basis</t>
+          <t>Why per-show moved</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>promoter contains 'Live Nation'. '(In-House Promotion)' alone is not counted.</t>
+          <t>Gross per show = avg ticket price x tickets per show. The two change % columns decompose the move into a price and a volume effect.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Venue type</t>
+          <t>Mix caveat</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>companyType when exactly Stadium/Amphitheatre, else venue-name keyword.</t>
+          <t>POST Aug 25 is the tail of the season, so act/venue mix shifts. Compare categories and LiveNation vs Market before concluding.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>Live Nation basis</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>promoter contains 'Live Nation'. '(In-House Promotion)' alone is not counted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Unmapped types</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>companyType is used first; the venue-name keyword is a gap filler only when companyType is blank or not one of the mapped types.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>Blanks</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Empty cell = zero denominator on that side, not a zero value.</t>
         </is>

--- a/gross_per_show_cutoff_comp.xlsx
+++ b/gross_per_show_cutoff_comp.xlsx
@@ -471,15 +471,15 @@
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gross per show, PRE vs POST 8/25. PRE = on or before Aug 25.</t>
+          <t>Gross per show, PRE vs POST 8/25. GROSS PER SHOW divides by numShows (performances). GROSS PER ENGAGEMENT divides by rows.</t>
         </is>
       </c>
     </row>
@@ -501,64 +501,64 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>engagements PRE</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>engagements POST</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>shows PRE</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>shows POST</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>gross_per_show PRE</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>gross_per_show POST</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>gross_per_engagement PRE</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>gross_per_engagement POST</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>avg_ticket_price PRE</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>avg_ticket_price POST</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>tickets_per_show PRE</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>tickets_per_show POST</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>engagements PRE</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>engagements POST</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>shows PRE</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>shows POST</t>
-        </is>
-      </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
           <t>tickets PRE</t>
@@ -581,17 +581,17 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>Gross/Show Change %</t>
+          <t>Gross/Show Chg %</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>Avg Ticket Price Change %</t>
+          <t>Tix Price Chg %</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>Tickets/Show Change %</t>
+          <t>Tix/Show Chg %</t>
         </is>
       </c>
     </row>
@@ -610,40 +610,40 @@
         <v>2024</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>1629</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>709</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1725</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>857</v>
+      </c>
+      <c r="H3" s="3" t="n">
         <v>523794</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="I3" s="3" t="n">
         <v>474889</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>554662</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>574020</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="L3" s="3" t="n">
         <v>66.89</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="M3" s="3" t="n">
         <v>70.73999999999999</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="N3" s="3" t="n">
         <v>7830.7</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="O3" s="3" t="n">
         <v>6713.2</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>1629</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>709</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>1725</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>857</v>
       </c>
       <c r="P3" s="3" t="n">
         <v>13508033</v>
@@ -682,40 +682,40 @@
         <v>2025</v>
       </c>
       <c r="D4" s="3" t="n">
+        <v>1389</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>589</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1455</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>631</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>480371</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="I4" s="3" t="n">
         <v>507385</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>503196</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="K4" s="3" t="n">
         <v>543565</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="L4" s="3" t="n">
         <v>66.81</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="M4" s="3" t="n">
         <v>72.31</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="N4" s="3" t="n">
         <v>7190.1</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="O4" s="3" t="n">
         <v>7017.2</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>1389</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>589</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>1455</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>631</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>10461654</v>
@@ -754,40 +754,40 @@
         <v>2024</v>
       </c>
       <c r="D5" s="3" t="n">
+        <v>1048</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>381</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1231</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>523</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <v>2814214</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="I5" s="3" t="n">
         <v>2646704</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="J5" s="3" t="n">
         <v>3305627</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="K5" s="3" t="n">
         <v>3633140</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="L5" s="3" t="n">
         <v>114.35</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="M5" s="3" t="n">
         <v>106.02</v>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="N5" s="3" t="n">
         <v>24610.9</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="O5" s="3" t="n">
         <v>24963.8</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>1048</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>381</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>1231</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>523</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>30296051</v>
@@ -826,40 +826,40 @@
         <v>2025</v>
       </c>
       <c r="D6" s="3" t="n">
+        <v>1131</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>376</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1374</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>513</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>3487999</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="I6" s="3" t="n">
         <v>2897575</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>4237410</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="K6" s="3" t="n">
         <v>3953340</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="L6" s="3" t="n">
         <v>126.31</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="M6" s="3" t="n">
         <v>112.4</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="N6" s="3" t="n">
         <v>27614.6</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="O6" s="3" t="n">
         <v>25779</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>1131</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>376</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>1374</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>513</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>37942458</v>
@@ -898,52 +898,52 @@
         <v>2024</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>736276</v>
+        <v>5659</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>688772</v>
+        <v>4004</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>948653</v>
+        <v>7287</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>827975</v>
+        <v>4811</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>96.04000000000001</v>
+        <v>734986</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>90.03</v>
+        <v>687609</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>7666.7</v>
+        <v>946429</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>7650.2</v>
+        <v>826196</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>5644</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>3993</v>
+        <v>90</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>7272</v>
+        <v>7655.6</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>4800</v>
+        <v>7639.7</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>55752318</v>
+        <v>55786557</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>36721156</v>
+        <v>36754815</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>5354196309.34</v>
+        <v>5355844199.84</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3306103290.62</v>
+        <v>3308089216.17</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>-0.0645</v>
@@ -952,7 +952,7 @@
         <v>-0.0626</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.0022</v>
+        <v>-0.0021</v>
       </c>
     </row>
     <row r="8">
@@ -970,61 +970,61 @@
         <v>2025</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>717993</v>
+        <v>5282</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>779913</v>
+        <v>3755</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>883610</v>
+        <v>6500</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>923209</v>
+        <v>4444</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>92.04000000000001</v>
+        <v>717507</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>91.7</v>
+        <v>779234</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>7800.8</v>
+        <v>882960</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>8505</v>
+        <v>922215</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>5276</v>
+        <v>92.03</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>3750</v>
+        <v>91.69</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>6493</v>
+        <v>7796.1</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>4439</v>
+        <v>8498.5</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>50650580</v>
+        <v>50674772</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>37753708</v>
+        <v>37767252</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>4661928547.74</v>
+        <v>4663793885.7</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>3462032049.73</v>
+        <v>3462916298.62</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.0862</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="U8" s="4" t="n">
         <v>-0.0037</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0901</v>
       </c>
     </row>
     <row r="9">
@@ -1042,61 +1042,61 @@
         <v>2024</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>108860</v>
+        <v>13062</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>106580</v>
+        <v>9197</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>140251</v>
+        <v>16824</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>141790</v>
+        <v>12232</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>69.03</v>
+        <v>108872</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>70.86</v>
+        <v>106567</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>1577</v>
+        <v>140228</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>1504</v>
+        <v>141734</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>13046</v>
+        <v>69</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>9187</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>16808</v>
+        <v>1577.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>12222</v>
+        <v>1504.1</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>26505933</v>
+        <v>26544716</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>18381785</v>
+        <v>18398455</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1829710810.81</v>
+        <v>1831657716.21</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1302620453.81</v>
+        <v>1303523260.09</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.0209</v>
+        <v>-0.0212</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.0265</v>
+        <v>0.0268</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.0463</v>
+        <v>-0.0467</v>
       </c>
     </row>
     <row r="10">
@@ -1114,61 +1114,61 @@
         <v>2025</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>106536</v>
+        <v>13371</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>115486</v>
+        <v>8800</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>135221</v>
+        <v>16971</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>149693</v>
+        <v>11405</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>71.39</v>
+        <v>106553</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>74.75</v>
+        <v>115524</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1492.3</v>
+        <v>135241</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1545</v>
+        <v>149722</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>13359</v>
+        <v>71.37</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>8788</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>16956</v>
+        <v>1493</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>11391</v>
+        <v>1545.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>25304100</v>
+        <v>25337345</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>17599038</v>
+        <v>17629607</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>1806417103.97</v>
+        <v>1808311812.05</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>1315500274.67</v>
+        <v>1317551577.6</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.0842</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.0471</v>
+        <v>0.0472</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.0353</v>
+        <v>0.0354</v>
       </c>
     </row>
     <row r="11">
@@ -1186,40 +1186,40 @@
         <v>2024</v>
       </c>
       <c r="D11" s="3" t="n">
+        <v>15081</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>8956</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>15716</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>9235</v>
+      </c>
+      <c r="H11" s="3" t="n">
         <v>21901</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="I11" s="3" t="n">
         <v>25050</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="J11" s="3" t="n">
         <v>22824</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="K11" s="3" t="n">
         <v>25830</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="L11" s="3" t="n">
         <v>40.03</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="M11" s="3" t="n">
         <v>42.7</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="N11" s="3" t="n">
         <v>547.1</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="O11" s="3" t="n">
         <v>586.6</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>15081</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>8956</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>15716</v>
-      </c>
-      <c r="O11" s="3" t="n">
-        <v>9235</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>8598514</v>
@@ -1258,40 +1258,40 @@
         <v>2025</v>
       </c>
       <c r="D12" s="3" t="n">
+        <v>13602</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>7593</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>14134</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>7895</v>
+      </c>
+      <c r="H12" s="3" t="n">
         <v>22907</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="I12" s="3" t="n">
         <v>25846</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="J12" s="3" t="n">
         <v>23803</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="K12" s="3" t="n">
         <v>26874</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="L12" s="3" t="n">
         <v>42.6</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="M12" s="3" t="n">
         <v>44.64</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="N12" s="3" t="n">
         <v>537.7</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="O12" s="3" t="n">
         <v>578.9</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>13602</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>7593</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>14134</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>7895</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>7600436</v>
@@ -1330,61 +1330,61 @@
         <v>2024</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>238041</v>
+        <v>2482</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>111855</v>
+        <v>1317</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>258596</v>
+        <v>2699</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>133674</v>
+        <v>1578</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>75.86</v>
+        <v>239443</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>63.08</v>
+        <v>111513</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>3137.8</v>
+        <v>260377</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>1773.3</v>
+        <v>133612</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>2513</v>
+        <v>76.09</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>1338</v>
+        <v>63.18</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>2730</v>
+        <v>3146.8</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>1599</v>
+        <v>1765</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>8566101</v>
+        <v>8493079</v>
       </c>
       <c r="Q13" s="3" t="n">
-        <v>2835506</v>
+        <v>2785177</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>649851513</v>
+        <v>646256717.1</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>178855982.14</v>
+        <v>175967250.31</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.5301</v>
+        <v>-0.5343</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.1685</v>
+        <v>-0.1697</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.4349</v>
+        <v>-0.4391</v>
       </c>
     </row>
     <row r="14">
@@ -1402,61 +1402,61 @@
         <v>2025</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>231171</v>
+        <v>2394</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>211538</v>
+        <v>1203</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>277462</v>
+        <v>2873</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>230612</v>
+        <v>1311</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>86.78</v>
+        <v>231632</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>81.59</v>
+        <v>212365</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>2663.9</v>
+        <v>277978</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>2592.8</v>
+        <v>231430</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>2412</v>
+        <v>86.94</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1220</v>
+        <v>81.78</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>2895</v>
+        <v>2664.3</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>1330</v>
+        <v>2596.7</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>7712077</v>
+        <v>7654640</v>
       </c>
       <c r="Q14" s="3" t="n">
-        <v>3448424</v>
+        <v>3404311</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>669238917.8099999</v>
+        <v>665478871.77</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>281346113.63</v>
+        <v>278410561.81</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.0849</v>
+        <v>-0.0832</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.0598</v>
+        <v>-0.0594</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.0267</v>
+        <v>-0.0254</v>
       </c>
     </row>
     <row r="15">
@@ -1474,40 +1474,40 @@
         <v>2024</v>
       </c>
       <c r="D15" s="3" t="n">
+        <v>38961</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>24564</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>45482</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>29236</v>
+      </c>
+      <c r="H15" s="3" t="n">
         <v>275841</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="I15" s="3" t="n">
         <v>232936</v>
       </c>
-      <c r="F15" s="3" t="n">
+      <c r="J15" s="3" t="n">
         <v>322009</v>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="K15" s="3" t="n">
         <v>277240</v>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="L15" s="3" t="n">
         <v>87.59</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="M15" s="3" t="n">
         <v>82.88</v>
       </c>
-      <c r="J15" s="3" t="n">
+      <c r="N15" s="3" t="n">
         <v>3149.1</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="O15" s="3" t="n">
         <v>2810.4</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>38961</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>24564</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>45482</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>29236</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>143226950</v>
@@ -1546,40 +1546,40 @@
         <v>2025</v>
       </c>
       <c r="D16" s="3" t="n">
+        <v>37169</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>22316</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>26199</v>
+      </c>
+      <c r="H16" s="3" t="n">
         <v>299092</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="I16" s="3" t="n">
         <v>269840</v>
       </c>
-      <c r="F16" s="3" t="n">
+      <c r="J16" s="3" t="n">
         <v>348484</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="K16" s="3" t="n">
         <v>316793</v>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="L16" s="3" t="n">
         <v>92.73999999999999</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="M16" s="3" t="n">
         <v>87.25</v>
       </c>
-      <c r="J16" s="3" t="n">
+      <c r="N16" s="3" t="n">
         <v>3225.1</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="O16" s="3" t="n">
         <v>3092.6</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>37169</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>22316</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>43307</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>26199</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>139671305</v>
@@ -1618,61 +1618,61 @@
         <v>2024</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>729365</v>
+        <v>806</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>759504</v>
+        <v>338</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>756819</v>
+        <v>836</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>789065</v>
+        <v>351</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>65.25</v>
+        <v>726039</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>69.97</v>
+        <v>751505</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>11177.6</v>
+        <v>753063</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>10855.3</v>
+        <v>780409</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>797</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>334</v>
+        <v>69.91</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>827</v>
+        <v>11109.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>347</v>
+        <v>10749.7</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>9243903</v>
+        <v>9287777</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>3766778</v>
+        <v>3773144</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>603185039.86</v>
+        <v>606968624.39</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>263547808.85</v>
+        <v>263778101.54</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.0413</v>
+        <v>0.0351</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.0723</v>
+        <v>0.0698</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.0288</v>
+        <v>-0.0324</v>
       </c>
     </row>
     <row r="18">
@@ -1690,61 +1690,61 @@
         <v>2025</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>647028</v>
+        <v>653</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>681944</v>
+        <v>286</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>664055</v>
+        <v>670</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>715799</v>
+        <v>300</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>62.98</v>
+        <v>644553</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>69.89</v>
+        <v>686464</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>10273.2</v>
+        <v>661333</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>9757.700000000001</v>
+        <v>720068</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>646</v>
+        <v>63.1</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>282</v>
+        <v>70.36</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>663</v>
+        <v>10214.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>296</v>
+        <v>9755.9</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>6811144</v>
+        <v>6843614</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>2888267</v>
+        <v>2926767</v>
       </c>
       <c r="R18" s="3" t="n">
-        <v>428979388.41</v>
+        <v>431850387.35</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>201855294.24</v>
+        <v>205939343.75</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.054</v>
+        <v>0.065</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.1097</v>
+        <v>0.1151</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.0502</v>
+        <v>-0.0449</v>
       </c>
     </row>
     <row r="19">
@@ -1762,61 +1762,61 @@
         <v>2024</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>4586633</v>
+        <v>254</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>5200285</v>
+        <v>159</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5878015</v>
+        <v>324</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>6465219</v>
+        <v>204</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>121.78</v>
+        <v>4418962</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>123.48</v>
+        <v>4476617</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>37662.8</v>
+        <v>5636787</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>42114.7</v>
+        <v>5743584</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>206</v>
+        <v>117.22</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>111</v>
+        <v>111.23</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>264</v>
+        <v>37698.8</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>138</v>
+        <v>40246.5</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>9942975</v>
+        <v>12214422</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>5811832</v>
+        <v>8210295</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>1210871081.01</v>
+        <v>1431743843.1</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>717639266.29</v>
+        <v>913229821.76</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.1338</v>
+        <v>0.013</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.014</v>
+        <v>-0.0511</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.1182</v>
+        <v>0.06759999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1834,61 +1834,61 @@
         <v>2025</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>6212065</v>
+        <v>498</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>5202382</v>
+        <v>168</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>8153335</v>
+        <v>643</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>6470189</v>
+        <v>208</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>145.96</v>
+        <v>4992822</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>126.38</v>
+        <v>4642548</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>42560.1</v>
+        <v>6446556</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>41164.1</v>
+        <v>5747916</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>368</v>
+        <v>140.06</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>119</v>
+        <v>118.77</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>483</v>
+        <v>35647.5</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>148</v>
+        <v>39089.9</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>20556542</v>
+        <v>22921351</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>6092282</v>
+        <v>8130690</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>3000427428.5</v>
+        <v>3210384812.03</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>769952463.3099999</v>
+        <v>965649906.34</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.1625</v>
+        <v>-0.0702</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.1341</v>
+        <v>-0.152</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.0328</v>
+        <v>0.09660000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1906,61 +1906,61 @@
         <v>2024</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1384801</v>
+        <v>1710</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1125284</v>
+        <v>1265</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1555317</v>
+        <v>1935</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1256648</v>
+        <v>1406</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>130.96</v>
+        <v>1325427</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>111.12</v>
+        <v>1084891</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>10574.6</v>
+        <v>1499825</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10126.8</v>
+        <v>1205816</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>1608</v>
+        <v>128</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>1165</v>
+        <v>107.56</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1806</v>
+        <v>10355</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1301</v>
+        <v>10086.3</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>19097696</v>
+        <v>20036936</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>13174980</v>
+        <v>14181298</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>2500949906.61</v>
+        <v>2564701174.53</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>1463994734</v>
+        <v>1525357187.01</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.1874</v>
+        <v>-0.1815</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.1515</v>
+        <v>-0.1597</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.0423</v>
+        <v>-0.0259</v>
       </c>
     </row>
     <row r="22">
@@ -1978,61 +1978,61 @@
         <v>2025</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1215271</v>
+        <v>1326</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1108463</v>
+        <v>1090</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1329975</v>
+        <v>1459</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1245154</v>
+        <v>1261</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>116.39</v>
+        <v>1176653</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>110.04</v>
+        <v>1052356</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>10441.4</v>
+        <v>1294674</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>10072.9</v>
+        <v>1217451</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>1229</v>
+        <v>113.56</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>965</v>
+        <v>105.99</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1345</v>
+        <v>10361.2</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>1084</v>
+        <v>9928.9</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>14043732</v>
+        <v>15117016</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>10918998</v>
+        <v>12520293</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>1634539612.31</v>
+        <v>1716737366.53</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1201573658.64</v>
+        <v>1327021095.93</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.1056</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.0546</v>
+        <v>-0.0667</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.0353</v>
+        <v>-0.0417</v>
       </c>
     </row>
     <row r="23">
@@ -2050,61 +2050,61 @@
         <v>2024</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>191089</v>
+        <v>1751</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>177217</v>
+        <v>1184</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>219416</v>
+        <v>2213</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>196019</v>
+        <v>1484</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>86.73999999999999</v>
+        <v>170755</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>83.37</v>
+        <v>157214</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2203.1</v>
+        <v>215808</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2125.8</v>
+        <v>197048</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1248</v>
+        <v>75.72</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>886</v>
+        <v>76.23</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1433</v>
+        <v>2255.1</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>980</v>
+        <v>2062.3</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3156999</v>
+        <v>4990435</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>2083241</v>
+        <v>3060470</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>273831139.93</v>
+        <v>377880476.31</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>173673025.16</v>
+        <v>233305270.98</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.0726</v>
+        <v>-0.0793</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.0389</v>
+        <v>0.0067</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.0351</v>
+        <v>-0.08550000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -2122,61 +2122,61 @@
         <v>2025</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>179668</v>
+        <v>1501</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>168936</v>
+        <v>1114</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>196720</v>
+        <v>1789</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>192274</v>
+        <v>1469</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>84.04000000000001</v>
+        <v>176013</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>81.31</v>
+        <v>159430</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>2138</v>
+        <v>209785</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>2077.7</v>
+        <v>210235</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>1159</v>
+        <v>78.13</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>789</v>
+        <v>77.23</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1269</v>
+        <v>2252.9</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>898</v>
+        <v>2064.3</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>2713110</v>
+        <v>4030490</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>1865813</v>
+        <v>3032408</v>
       </c>
       <c r="R24" s="3" t="n">
-        <v>227998562.64</v>
+        <v>314887776.81</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>151704349.46</v>
+        <v>234202216.73</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.0597</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.0325</v>
+        <v>-0.0115</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.0282</v>
+        <v>-0.0837</v>
       </c>
     </row>
     <row r="25">
@@ -2194,61 +2194,61 @@
         <v>2024</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>54991</v>
+        <v>1597</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>62743</v>
+        <v>1108</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>56544</v>
+        <v>1628</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>64174</v>
+        <v>1133</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>48.54</v>
+        <v>38591</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>54.63</v>
+        <v>42377</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1132.9</v>
+        <v>39340</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>1148.4</v>
+        <v>43333</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>850</v>
+        <v>45.23</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>570</v>
+        <v>49.23</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>874</v>
+        <v>853.2</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>583</v>
+        <v>860.8</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>990168</v>
+        <v>1388965</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>669542</v>
+        <v>975275</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>48062548.65</v>
+        <v>62825880.14</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>36579334.52</v>
+        <v>48012720.84</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>0.141</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.1255</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.0137</v>
+        <v>0.0089</v>
       </c>
     </row>
     <row r="26">
@@ -2266,61 +2266,61 @@
         <v>2025</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>55976</v>
+        <v>1613</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>50586</v>
+        <v>1060</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>57274</v>
+        <v>1650</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>51396</v>
+        <v>1076</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>49.53</v>
+        <v>38099</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>48.65</v>
+        <v>36350</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>1130.1</v>
+        <v>38973</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>1039.9</v>
+        <v>36899</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>863</v>
+        <v>45.76</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>562</v>
+        <v>45.95</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>883</v>
+        <v>832.6</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>571</v>
+        <v>791</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>997874</v>
+        <v>1373788</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>593767</v>
+        <v>851131</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>49427128.85</v>
+        <v>62863821.82</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>28884763.54</v>
+        <v>39113037.23</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.0963</v>
+        <v>-0.0459</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.0178</v>
+        <v>0.0042</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.0798</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="27">
@@ -2338,61 +2338,61 @@
         <v>2024</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>664924</v>
+        <v>275</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>269244</v>
+        <v>160</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>678493</v>
+        <v>289</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>280308</v>
+        <v>228</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>91.73999999999999</v>
+        <v>392005</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>73.36</v>
+        <v>154338</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>7248.2</v>
+        <v>411962</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>3670.3</v>
+        <v>219931</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>98</v>
+        <v>73.48999999999999</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>73</v>
+        <v>58.59</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>100</v>
+        <v>5334.5</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>76</v>
+        <v>2634.1</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>724821</v>
+        <v>1541667</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>278943</v>
+        <v>600577</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>66492361.81</v>
+        <v>113289559.67</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>20462509</v>
+        <v>35188986.8</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.5951</v>
+        <v>-0.6063</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.2003</v>
+        <v>-0.2027</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.4936</v>
+        <v>-0.5062</v>
       </c>
     </row>
     <row r="28">
@@ -2410,61 +2410,61 @@
         <v>2025</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>645016</v>
+        <v>182</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>615375</v>
+        <v>132</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>651666</v>
+        <v>205</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>669355</v>
+        <v>142</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>91.3</v>
+        <v>446511</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>119.98</v>
+        <v>489859</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>7064.7</v>
+        <v>502938</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>5128.9</v>
+        <v>526970</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>97</v>
+        <v>82.7</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>57</v>
+        <v>98.67</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>98</v>
+        <v>5399</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>62</v>
+        <v>4964.7</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>692340</v>
+        <v>1106787</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>317992</v>
+        <v>704987</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>63211600.47</v>
+        <v>91534682.08</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>38153256.14</v>
+        <v>69559990.01000001</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.046</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.3141</v>
+        <v>0.1931</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-0.274</v>
+        <v>-0.0804</v>
       </c>
     </row>
     <row r="29">
@@ -2482,61 +2482,61 @@
         <v>2024</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>886763</v>
+        <v>6393</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>781284</v>
+        <v>4214</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>978446</v>
+        <v>7225</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>852468</v>
+        <v>4806</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>108.98</v>
+        <v>713828</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>103.78</v>
+        <v>628147</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>8136.6</v>
+        <v>806728</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>7528.6</v>
+        <v>716391</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>4807</v>
+        <v>104.27</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>3139</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>5304</v>
+        <v>6845.7</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>3425</v>
+        <v>6408.9</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>43156562</v>
+        <v>49460202</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>25785316</v>
+        <v>30801059</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>4703392077.87</v>
+        <v>5157409558.14</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>2675896677.82</v>
+        <v>3018872088.93</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1189</v>
+        <v>-0.12</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.0477</v>
+        <v>-0.06</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.0747</v>
+        <v>-0.0638</v>
       </c>
     </row>
     <row r="30">
@@ -2554,61 +2554,61 @@
         <v>2025</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1139967</v>
+        <v>5773</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>781995</v>
+        <v>3850</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1239015</v>
+        <v>6416</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>862337</v>
+        <v>4456</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>117.97</v>
+        <v>908394</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>105.49</v>
+        <v>637676</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>9663.5</v>
+        <v>1009572</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>7413.2</v>
+        <v>738048</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>4362</v>
+        <v>113.41</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>2774</v>
+        <v>100.88</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>4741</v>
+        <v>8010.1</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>3059</v>
+        <v>6321</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>45814742</v>
+        <v>51393046</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>22677119</v>
+        <v>28166276</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>5404583721.18</v>
+        <v>5828258846.62</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>2392123785.33</v>
+        <v>2841485589.99</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.314</v>
+        <v>-0.298</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.1058</v>
+        <v>-0.1105</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.2329</v>
+        <v>-0.2109</v>
       </c>
     </row>
   </sheetData>
@@ -2622,11 +2622,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="105" customWidth="1" min="2" max="2"/>
+    <col width="108" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2644,130 +2644,118 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Gross per show = SUM(grossUSD) / SUM(numShows) for one basis x category x year x pre/post cell. grossUSD is a whole-run total (verified: grossUSD = avgGrossUSD * numShows).</t>
+          <t>ONE ROW = ONE ENGAGEMENT. numShows = performances inside it. grossUSD is a whole-run total (verified grossUSD = avgGrossUSD * numShows).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Categories</t>
+          <t>Gross per show</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>The six pipeline categories from post_aug25_capacity.py: Amphitheatre, Stadium, Arena, Theater, Club, Other. 'All' adds the six.</t>
+          <t>SUM(grossUSD) / SUM(numShows). Performances in the denominator.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Other bucket</t>
+          <t>Gross per engagement</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Pollstar has 13 companyType values; this taxonomy keeps five. Casino, Convention Center, Complex, Outdoor Venues, Festival, Theme Park, Streaming Online and Promoter all fall to Other. A large Other is a sign the taxonomy does not fit the source, not a data error.</t>
+          <t>SUM(grossUSD) / row count. Engagements in the denominator. Reported so the two units can never be confused.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Cutoff</t>
+          <t>Live Nation basis</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>PRE = eventDate on or before Aug 25 of the show year; POST = after.</t>
+          <t>The same ten promoter names as generate_lyv_datasets.py: Live Nation, OCESA, C3, Cuffe &amp; Taylor, DF Concerts, Emporium Presents, Festival Republic, Frank Productions, House of Blues, MCD. 'Market' is every promoter.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Reconciles with</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>pollstar/concerts.csv (data ends 2026-08-16). 2024 and 2025 settled both sides.</t>
+          <t>LYV_summary_all_years.xlsx / venue_matches_summary.xlsx on the LiveNation full-year sum(numShows) per year, subject to the venue taxonomy below.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Grain</t>
+          <t>Categories</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>ONE ROW = ONE ENGAGEMENT. numShows = performances inside it.</t>
+          <t>Six pipeline categories. Pollstar companyType is the authority; venue-name keyword is a gap filler. Cuffe &amp; Taylor, Festival Republic, OCESA, MCD etc. are promoters, not venue types, and are unaffected by that mapping.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Why per-show moved</t>
+          <t>Cutoff</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Gross per show = avg ticket price x tickets per show. The two change % columns decompose the move into a price and a volume effect.</t>
+          <t>PRE = eventDate on or before Aug 25 of the show year; POST = after.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mix caveat</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>POST Aug 25 is the tail of the season, so act/venue mix shifts. Compare categories and LiveNation vs Market before concluding.</t>
+          <t>pollstar/concerts.csv, data ends 2026-08-16. 2024 and 2025 settled both sides.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Live Nation basis</t>
+          <t>Why per-show moved</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>promoter contains 'Live Nation'. '(In-House Promotion)' alone is not counted.</t>
+          <t>Gross per show = avg ticket price x tickets per show. Those two change % columns decompose the move into price and volume.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Unmapped types</t>
+          <t>Blanks</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>companyType is used first; the venue-name keyword is a gap filler only when companyType is blank or not one of the mapped types.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Blanks</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Empty cell = zero denominator on that side, not a zero value.</t>
         </is>
